--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ34"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2520,10 +2520,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132520210</v>
+        <v>136621037</v>
       </c>
       <c r="B20" t="n">
-        <v>80499</v>
+        <v>80593</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2531,37 +2531,40 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>620977</v>
+        <v>621035</v>
       </c>
       <c r="R20" t="n">
-        <v>6876427</v>
+        <v>6876418</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2585,12 +2588,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:34</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt på mossklädd lodyta.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2605,27 +2623,27 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132520210</t>
+          <t>https://artportalen.se/Sighting/136621037</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131116436</v>
+        <v>132520210</v>
       </c>
       <c r="B21" t="n">
-        <v>57950</v>
+        <v>80499</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2633,21 +2651,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6463</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2657,10 +2675,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>620927</v>
+        <v>620977</v>
       </c>
       <c r="R21" t="n">
-        <v>6876471</v>
+        <v>6876427</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2687,12 +2705,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2718,16 +2736,16 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131116436</t>
+          <t>https://artportalen.se/Sighting/132520210</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132518532</v>
+        <v>131116436</v>
       </c>
       <c r="B22" t="n">
-        <v>57972</v>
+        <v>57950</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2755,14 +2773,14 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>620884</v>
+        <v>620927</v>
       </c>
       <c r="R22" t="n">
-        <v>6876450</v>
+        <v>6876471</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2789,12 +2807,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2820,13 +2838,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132518532</t>
+          <t>https://artportalen.se/Sighting/131116436</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132518954</v>
+        <v>132518532</v>
       </c>
       <c r="B23" t="n">
         <v>57972</v>
@@ -2857,14 +2875,14 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>620862</v>
+        <v>620884</v>
       </c>
       <c r="R23" t="n">
-        <v>6876352</v>
+        <v>6876450</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2922,13 +2940,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132518954</t>
+          <t>https://artportalen.se/Sighting/132518532</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132520555</v>
+        <v>132518954</v>
       </c>
       <c r="B24" t="n">
         <v>57972</v>
@@ -2959,14 +2977,14 @@
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>620991</v>
+        <v>620862</v>
       </c>
       <c r="R24" t="n">
-        <v>6876463</v>
+        <v>6876352</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3024,33 +3042,33 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132520555</t>
+          <t>https://artportalen.se/Sighting/132518954</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131117304</v>
+        <v>132520555</v>
       </c>
       <c r="B25" t="n">
-        <v>57953</v>
+        <v>57972</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3061,14 +3079,14 @@
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>621008</v>
+        <v>620991</v>
       </c>
       <c r="R25" t="n">
-        <v>6876450</v>
+        <v>6876463</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3095,12 +3113,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3126,71 +3144,51 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131117304</t>
+          <t>https://artportalen.se/Sighting/132520555</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131117093</v>
+        <v>131117304</v>
       </c>
       <c r="B26" t="n">
-        <v>57141</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>620943</v>
+        <v>621008</v>
       </c>
       <c r="R26" t="n">
-        <v>6876466</v>
+        <v>6876450</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3248,56 +3246,71 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131117093</t>
+          <t>https://artportalen.se/Sighting/131117304</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132518566</v>
+        <v>131117093</v>
       </c>
       <c r="B27" t="n">
-        <v>5484</v>
+        <v>57141</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>101920</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>620837</v>
+        <v>620943</v>
       </c>
       <c r="R27" t="n">
-        <v>6876306</v>
+        <v>6876466</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3324,12 +3337,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3338,7 +3351,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3356,56 +3368,56 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132518566</t>
+          <t>https://artportalen.se/Sighting/131117093</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132518067</v>
+        <v>132518566</v>
       </c>
       <c r="B28" t="n">
-        <v>57165</v>
+        <v>5484</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102613</v>
+        <v>101920</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>620884</v>
+        <v>620837</v>
       </c>
       <c r="R28" t="n">
-        <v>6876450</v>
+        <v>6876306</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3446,6 +3458,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3463,13 +3476,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132518067</t>
+          <t>https://artportalen.se/Sighting/132518566</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132520291</v>
+        <v>132518067</v>
       </c>
       <c r="B29" t="n">
         <v>57165</v>
@@ -3497,36 +3510,22 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="M29" t="inlineStr">
         <is>
-          <t>stationär</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Hls</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>621111</v>
+        <v>620884</v>
       </c>
       <c r="R29" t="n">
-        <v>6876464</v>
+        <v>6876450</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3584,33 +3583,33 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132520291</t>
+          <t>https://artportalen.se/Sighting/132518067</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132736947</v>
+        <v>132520291</v>
       </c>
       <c r="B30" t="n">
-        <v>57816</v>
+        <v>57165</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102621</v>
+        <v>102613</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3620,34 +3619,37 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>i par</t>
+          <t>hane</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>parning/parningsceremonier</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>620999</v>
+        <v>621111</v>
       </c>
       <c r="R30" t="n">
-        <v>6876426</v>
+        <v>6876464</v>
       </c>
       <c r="S30" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3671,27 +3673,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>08:41</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>10:04</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Hanen överlämnade byte.</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3706,27 +3693,27 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Magnus Lilja</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Johan Myhrer</t>
+          <t>Magnus Lilja</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132736947</t>
+          <t>https://artportalen.se/Sighting/132520291</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132518000</v>
+        <v>132736947</v>
       </c>
       <c r="B31" t="n">
-        <v>57386</v>
+        <v>57816</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3734,16 +3721,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102954</v>
+        <v>102621</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3751,25 +3738,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>parning/parningsceremonier</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
+          <t>Myckelmyrberget, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>620870</v>
+        <v>620999</v>
       </c>
       <c r="R31" t="n">
-        <v>6876468</v>
+        <v>6876426</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3793,12 +3791,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>08:41</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>10:04</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Hanen överlämnade byte.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3813,27 +3826,27 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Magnus Lilja</t>
+          <t>Johan Myhrer</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132518000</t>
+          <t>https://artportalen.se/Sighting/132736947</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132519214</v>
+        <v>132518000</v>
       </c>
       <c r="B32" t="n">
-        <v>58136</v>
+        <v>57386</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3841,34 +3854,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>103021</v>
+        <v>102954</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+          <t>Myckelmyrberget, Håckstatjärnen, Jättendal, Hls</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>620896</v>
+        <v>620870</v>
       </c>
       <c r="R32" t="n">
-        <v>6876396</v>
+        <v>6876468</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3926,16 +3944,16 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/132519214</t>
+          <t>https://artportalen.se/Sighting/132518000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131116531</v>
+        <v>132519214</v>
       </c>
       <c r="B33" t="n">
-        <v>56522</v>
+        <v>58136</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3943,21 +3961,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3967,10 +3985,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>620966</v>
+        <v>620896</v>
       </c>
       <c r="R33" t="n">
-        <v>6876458</v>
+        <v>6876396</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3997,12 +4015,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4028,38 +4046,38 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131116531</t>
+          <t>https://artportalen.se/Sighting/132519214</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132519505</v>
+        <v>131116531</v>
       </c>
       <c r="B34" t="n">
-        <v>99195</v>
+        <v>56522</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>206004</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4069,10 +4087,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>620931</v>
+        <v>620966</v>
       </c>
       <c r="R34" t="n">
-        <v>6876407</v>
+        <v>6876458</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4099,12 +4117,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4129,6 +4147,108 @@
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131116531</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132519505</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Myckelmyrberget, Myckelmyrberget, Hls</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>620931</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6876407</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Nordanstig</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Jättendal</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Magnus Lilja</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/132519505</t>
         </is>
@@ -4169,6 +4289,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>136621037</v>
       </c>
       <c r="B20" t="n">
-        <v>80593</v>
+        <v>80595</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>136621037</v>
       </c>
       <c r="B20" t="n">
-        <v>80595</v>
+        <v>80599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>136621037</v>
       </c>
       <c r="B20" t="n">
-        <v>80599</v>
+        <v>80601</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>136621037</v>
       </c>
       <c r="B20" t="n">
-        <v>80601</v>
+        <v>80602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>136621037</v>
       </c>
       <c r="B20" t="n">
-        <v>80602</v>
+        <v>80604</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>136621037</v>
       </c>
       <c r="B20" t="n">
-        <v>80604</v>
+        <v>80607</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>136621037</v>
       </c>
       <c r="B20" t="n">
-        <v>80607</v>
+        <v>80620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 57296-2025 artfynd.xlsx
+++ b/artfynd/A 57296-2025 artfynd.xlsx
@@ -2523,7 +2523,7 @@
         <v>136621037</v>
       </c>
       <c r="B20" t="n">
-        <v>80620</v>
+        <v>80622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
